--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L683"/>
+  <dimension ref="A1:L685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29110,6 +29110,90 @@
       <c r="L683" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>240.51</v>
+      </c>
+      <c r="C684" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="D684" t="n">
+        <v>315.19</v>
+      </c>
+      <c r="E684" t="n">
+        <v>324.12</v>
+      </c>
+      <c r="F684" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="G684" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="H684" t="n">
+        <v>335.66</v>
+      </c>
+      <c r="I684" t="n">
+        <v>341.97</v>
+      </c>
+      <c r="J684" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="K684" t="n">
+        <v>344.85</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="C685" t="n">
+        <v>329.43</v>
+      </c>
+      <c r="D685" t="n">
+        <v>319.41</v>
+      </c>
+      <c r="E685" t="n">
+        <v>325.07</v>
+      </c>
+      <c r="F685" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="G685" t="n">
+        <v>332.84</v>
+      </c>
+      <c r="H685" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="I685" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="J685" t="n">
+        <v>344.36</v>
+      </c>
+      <c r="K685" t="n">
+        <v>344.66</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29124,7 +29208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B712"/>
+  <dimension ref="A1:B714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36247,6 +36331,26 @@
       </c>
       <c r="B712" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -36415,28 +36519,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.081639331893142</v>
+        <v>-1.082020385076117</v>
       </c>
       <c r="J2" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K2" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01750392188691374</v>
+        <v>0.01762252335878178</v>
       </c>
       <c r="M2" t="n">
-        <v>47.71850452204816</v>
+        <v>47.60330335973507</v>
       </c>
       <c r="N2" t="n">
-        <v>2985.626526979345</v>
+        <v>2976.984114771558</v>
       </c>
       <c r="O2" t="n">
-        <v>54.64088695271468</v>
+        <v>54.56174589189351</v>
       </c>
       <c r="P2" t="n">
-        <v>278.6503192230516</v>
+        <v>278.6548081497364</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36493,28 +36597,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3269102440282817</v>
+        <v>-0.325430496817509</v>
       </c>
       <c r="J3" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K3" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1175246657702362</v>
+        <v>0.1171721623798219</v>
       </c>
       <c r="M3" t="n">
-        <v>4.858238195399148</v>
+        <v>4.850299065937203</v>
       </c>
       <c r="N3" t="n">
-        <v>38.18964159817131</v>
+        <v>38.09515192768753</v>
       </c>
       <c r="O3" t="n">
-        <v>6.179776824301287</v>
+        <v>6.172127018110332</v>
       </c>
       <c r="P3" t="n">
-        <v>335.4011500274557</v>
+        <v>335.3839630877819</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36571,28 +36675,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3804086217853857</v>
+        <v>-0.3801982529569065</v>
       </c>
       <c r="J4" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K4" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1562835765302705</v>
+        <v>0.156897863626859</v>
       </c>
       <c r="M4" t="n">
-        <v>4.832307270254815</v>
+        <v>4.824351126157292</v>
       </c>
       <c r="N4" t="n">
-        <v>37.17909694618331</v>
+        <v>37.08386835885153</v>
       </c>
       <c r="O4" t="n">
-        <v>6.097466436659025</v>
+        <v>6.089652564707738</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9946535279223</v>
+        <v>326.9921967270954</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36649,28 +36753,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.306776496938357</v>
+        <v>-0.3028253490447168</v>
       </c>
       <c r="J5" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K5" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1066346920574217</v>
+        <v>0.1044575829760439</v>
       </c>
       <c r="M5" t="n">
-        <v>4.861090533273596</v>
+        <v>4.864734878779172</v>
       </c>
       <c r="N5" t="n">
-        <v>37.52232188092428</v>
+        <v>37.53464204551118</v>
       </c>
       <c r="O5" t="n">
-        <v>6.125546659762236</v>
+        <v>6.126552215195034</v>
       </c>
       <c r="P5" t="n">
-        <v>326.2123462055689</v>
+        <v>326.1664553575828</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36727,28 +36831,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3418646649420982</v>
+        <v>-0.3397954939247654</v>
       </c>
       <c r="J6" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K6" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1752615996879445</v>
+        <v>0.1742090675313342</v>
       </c>
       <c r="M6" t="n">
-        <v>4.114651135333268</v>
+        <v>4.112445924886788</v>
       </c>
       <c r="N6" t="n">
-        <v>26.17296028199881</v>
+        <v>26.12980818154664</v>
       </c>
       <c r="O6" t="n">
-        <v>5.115951551959695</v>
+        <v>5.111732405119289</v>
       </c>
       <c r="P6" t="n">
-        <v>333.1734007186362</v>
+        <v>333.149370885951</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36805,28 +36909,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2229516395037373</v>
+        <v>-0.2211955130990286</v>
       </c>
       <c r="J7" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K7" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1258803901674067</v>
+        <v>0.1246577207679327</v>
       </c>
       <c r="M7" t="n">
-        <v>3.224263923817501</v>
+        <v>3.223277098312255</v>
       </c>
       <c r="N7" t="n">
-        <v>16.42665348501211</v>
+        <v>16.4026110621078</v>
       </c>
       <c r="O7" t="n">
-        <v>4.052980814784608</v>
+        <v>4.050013711348123</v>
       </c>
       <c r="P7" t="n">
-        <v>335.8999001567473</v>
+        <v>335.8795052118799</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36883,28 +36987,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08966695469151216</v>
+        <v>-0.08890651548078085</v>
       </c>
       <c r="J8" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K8" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03284701614868812</v>
+        <v>0.0324895105879629</v>
       </c>
       <c r="M8" t="n">
-        <v>2.709150003265153</v>
+        <v>2.705094356096435</v>
       </c>
       <c r="N8" t="n">
-        <v>11.26624172348113</v>
+        <v>11.23780077541705</v>
       </c>
       <c r="O8" t="n">
-        <v>3.356522266197728</v>
+        <v>3.352282919954258</v>
       </c>
       <c r="P8" t="n">
-        <v>336.8212848857817</v>
+        <v>336.8124530365824</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36961,28 +37065,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06630167919881243</v>
+        <v>-0.06462253517095742</v>
       </c>
       <c r="J9" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K9" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01573444923403511</v>
+        <v>0.01502476131243036</v>
       </c>
       <c r="M9" t="n">
-        <v>2.899127158670372</v>
+        <v>2.897471399220653</v>
       </c>
       <c r="N9" t="n">
-        <v>13.08653790549258</v>
+        <v>13.07035404998336</v>
       </c>
       <c r="O9" t="n">
-        <v>3.61753201858568</v>
+        <v>3.615294462417047</v>
       </c>
       <c r="P9" t="n">
-        <v>341.2026242225378</v>
+        <v>341.18312149383</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37039,28 +37143,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03515440486582817</v>
+        <v>0.03650723737202145</v>
       </c>
       <c r="J10" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K10" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006027178143696132</v>
+        <v>0.006526298144145293</v>
       </c>
       <c r="M10" t="n">
-        <v>2.486872449920402</v>
+        <v>2.486129903718024</v>
       </c>
       <c r="N10" t="n">
-        <v>9.69917855052276</v>
+        <v>9.686102086464608</v>
       </c>
       <c r="O10" t="n">
-        <v>3.114350421921522</v>
+        <v>3.112250325160977</v>
       </c>
       <c r="P10" t="n">
-        <v>340.6131887355246</v>
+        <v>340.5974733567483</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37117,28 +37221,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05923384314814006</v>
+        <v>0.05874368522334961</v>
       </c>
       <c r="J11" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K11" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01825332657139533</v>
+        <v>0.01806240330563924</v>
       </c>
       <c r="M11" t="n">
-        <v>2.397928624808919</v>
+        <v>2.393170841739043</v>
       </c>
       <c r="N11" t="n">
-        <v>8.980741768060254</v>
+        <v>8.95637701859569</v>
       </c>
       <c r="O11" t="n">
-        <v>2.996788575802479</v>
+        <v>2.992720671662441</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9934205653965</v>
+        <v>343.9991137730348</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37176,7 +37280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L683"/>
+  <dimension ref="A1:L685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79477,6 +79581,130 @@
         </is>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-45.529859517949546,170.7601543816431</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-45.53087101516985,170.7597955915727</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-45.531306694499314,170.7591263693434</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-45.53178797534521,170.75859539684583</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-45.532230733525616,170.7579589977704</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-45.53270052126171,170.7573497891407</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>-45.53316784506741,170.75674327075814</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>-45.533667233862346,170.7561891432231</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>-45.534178924339024,170.7556710979856</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>-45.53470394651318,170.75517554860033</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-45.530006398321866,170.76025147224848</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-45.530874162945004,170.75979921499203</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-45.531331881826695,170.75916679661935</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-45.53179430145224,170.7586035759432</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-45.53222844637658,170.75795610702602</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-45.532699802599176,170.75734882085393</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>-45.53316835245339,170.7567439972406</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>-45.53366999429944,170.7561937016593</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>-45.53418542613965,170.75568352337154</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>-45.5347029433176,170.7551735789381</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L685"/>
+  <dimension ref="A1:L688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29194,6 +29194,132 @@
       <c r="L685" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>311.55</v>
+      </c>
+      <c r="C686" t="n">
+        <v>331.01</v>
+      </c>
+      <c r="D686" t="n">
+        <v>324.32</v>
+      </c>
+      <c r="E686" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="F686" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="G686" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="H686" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="I686" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="J686" t="n">
+        <v>346.67</v>
+      </c>
+      <c r="K686" t="n">
+        <v>346.46</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>313.16</v>
+      </c>
+      <c r="C687" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="D687" t="n">
+        <v>322.65</v>
+      </c>
+      <c r="E687" t="n">
+        <v>325.41</v>
+      </c>
+      <c r="F687" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="G687" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="H687" t="n">
+        <v>337.92</v>
+      </c>
+      <c r="I687" t="n">
+        <v>343.78</v>
+      </c>
+      <c r="J687" t="n">
+        <v>345.72</v>
+      </c>
+      <c r="K687" t="n">
+        <v>345.44</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>314.97</v>
+      </c>
+      <c r="C688" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="D688" t="n">
+        <v>321.71</v>
+      </c>
+      <c r="E688" t="n">
+        <v>323.06</v>
+      </c>
+      <c r="F688" t="n">
+        <v>329.01</v>
+      </c>
+      <c r="G688" t="n">
+        <v>333.21</v>
+      </c>
+      <c r="H688" t="n">
+        <v>337.36</v>
+      </c>
+      <c r="I688" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="J688" t="n">
+        <v>345.33</v>
+      </c>
+      <c r="K688" t="n">
+        <v>345.34</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29208,7 +29334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B714"/>
+  <dimension ref="A1:B717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36351,6 +36477,36 @@
       </c>
       <c r="B714" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -36519,28 +36675,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.082020385076117</v>
+        <v>-1.021172740277755</v>
       </c>
       <c r="J2" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K2" t="n">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01762252335878178</v>
+        <v>0.0157838984791917</v>
       </c>
       <c r="M2" t="n">
-        <v>47.60330335973507</v>
+        <v>47.67665442370684</v>
       </c>
       <c r="N2" t="n">
-        <v>2976.984114771558</v>
+        <v>2981.333695878868</v>
       </c>
       <c r="O2" t="n">
-        <v>54.56174589189351</v>
+        <v>54.60159059843283</v>
       </c>
       <c r="P2" t="n">
-        <v>278.6548081497364</v>
+        <v>277.9226857553247</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36597,28 +36753,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.325430496817509</v>
+        <v>-0.3219335109155256</v>
       </c>
       <c r="J3" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K3" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1171721623798219</v>
+        <v>0.1157472590718361</v>
       </c>
       <c r="M3" t="n">
-        <v>4.850299065937203</v>
+        <v>4.843684836848442</v>
       </c>
       <c r="N3" t="n">
-        <v>38.09515192768753</v>
+        <v>37.99140651556642</v>
       </c>
       <c r="O3" t="n">
-        <v>6.172127018110332</v>
+        <v>6.163716939928896</v>
       </c>
       <c r="P3" t="n">
-        <v>335.3839630877819</v>
+        <v>335.3430238314005</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36675,28 +36831,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3801982529569065</v>
+        <v>-0.3746687198670409</v>
       </c>
       <c r="J4" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K4" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.156897863626859</v>
+        <v>0.1537199590682214</v>
       </c>
       <c r="M4" t="n">
-        <v>4.824351126157292</v>
+        <v>4.828504268700015</v>
       </c>
       <c r="N4" t="n">
-        <v>37.08386835885153</v>
+        <v>37.08224445603513</v>
       </c>
       <c r="O4" t="n">
-        <v>6.089652564707738</v>
+        <v>6.089519230286997</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9921967270954</v>
+        <v>326.9274673737825</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36753,28 +36909,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3028253490447168</v>
+        <v>-0.2965189052716489</v>
       </c>
       <c r="J5" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K5" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1044575829760439</v>
+        <v>0.1009283728238084</v>
       </c>
       <c r="M5" t="n">
-        <v>4.864734878779172</v>
+        <v>4.871778698341336</v>
       </c>
       <c r="N5" t="n">
-        <v>37.53464204551118</v>
+        <v>37.58141244224562</v>
       </c>
       <c r="O5" t="n">
-        <v>6.126552215195034</v>
+        <v>6.130368051124306</v>
       </c>
       <c r="P5" t="n">
-        <v>326.1664553575828</v>
+        <v>326.0926324667557</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36831,28 +36987,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3397954939247654</v>
+        <v>-0.3345459149694098</v>
       </c>
       <c r="J6" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K6" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1742090675313342</v>
+        <v>0.1703372578489968</v>
       </c>
       <c r="M6" t="n">
-        <v>4.112445924886788</v>
+        <v>4.119191693015925</v>
       </c>
       <c r="N6" t="n">
-        <v>26.12980818154664</v>
+        <v>26.15716668191483</v>
       </c>
       <c r="O6" t="n">
-        <v>5.111732405119289</v>
+        <v>5.114407754756638</v>
       </c>
       <c r="P6" t="n">
-        <v>333.149370885951</v>
+        <v>333.0879155097716</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36909,28 +37065,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2211955130990286</v>
+        <v>-0.2177733267940236</v>
       </c>
       <c r="J7" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K7" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1246577207679327</v>
+        <v>0.12190676811483</v>
       </c>
       <c r="M7" t="n">
-        <v>3.223277098312255</v>
+        <v>3.225411371528443</v>
       </c>
       <c r="N7" t="n">
-        <v>16.4026110621078</v>
+        <v>16.39115226222994</v>
       </c>
       <c r="O7" t="n">
-        <v>4.050013711348123</v>
+        <v>4.04859880233025</v>
       </c>
       <c r="P7" t="n">
-        <v>335.8795052118799</v>
+        <v>335.8394428234768</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36987,28 +37143,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08890651548078085</v>
+        <v>-0.08574984970761378</v>
       </c>
       <c r="J8" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K8" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0324895105879629</v>
+        <v>0.03043427804393184</v>
       </c>
       <c r="M8" t="n">
-        <v>2.705094356096435</v>
+        <v>2.708971207085156</v>
       </c>
       <c r="N8" t="n">
-        <v>11.23780077541705</v>
+        <v>11.24005109695115</v>
       </c>
       <c r="O8" t="n">
-        <v>3.352282919954258</v>
+        <v>3.352618543310758</v>
       </c>
       <c r="P8" t="n">
-        <v>336.8124530365824</v>
+        <v>336.775499276476</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37065,28 +37221,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06462253517095742</v>
+        <v>-0.06059583622354779</v>
       </c>
       <c r="J9" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K9" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01502476131243036</v>
+        <v>0.01327189644503179</v>
       </c>
       <c r="M9" t="n">
-        <v>2.897471399220653</v>
+        <v>2.900768115429734</v>
       </c>
       <c r="N9" t="n">
-        <v>13.07035404998336</v>
+        <v>13.09897704208252</v>
       </c>
       <c r="O9" t="n">
-        <v>3.615294462417047</v>
+        <v>3.619250895155311</v>
       </c>
       <c r="P9" t="n">
-        <v>341.18312149383</v>
+        <v>341.13598521096</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37143,28 +37299,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03650723737202145</v>
+        <v>0.04050562338499085</v>
       </c>
       <c r="J10" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K10" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006526298144145293</v>
+        <v>0.008029083888591249</v>
       </c>
       <c r="M10" t="n">
-        <v>2.486129903718024</v>
+        <v>2.494187736461662</v>
       </c>
       <c r="N10" t="n">
-        <v>9.686102086464608</v>
+        <v>9.72637222387073</v>
       </c>
       <c r="O10" t="n">
-        <v>3.112250325160977</v>
+        <v>3.11871323206715</v>
       </c>
       <c r="P10" t="n">
-        <v>340.5974733567483</v>
+        <v>340.5506662144759</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37221,28 +37377,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05874368522334961</v>
+        <v>0.05891426365435661</v>
       </c>
       <c r="J11" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K11" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01806240330563924</v>
+        <v>0.01833154723398023</v>
       </c>
       <c r="M11" t="n">
-        <v>2.393170841739043</v>
+        <v>2.384571940121089</v>
       </c>
       <c r="N11" t="n">
-        <v>8.95637701859569</v>
+        <v>8.918543229407048</v>
       </c>
       <c r="O11" t="n">
-        <v>2.992720671662441</v>
+        <v>2.986393013219634</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9991137730348</v>
+        <v>343.9971201064295</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37280,7 +37436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L685"/>
+  <dimension ref="A1:L688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79705,6 +79861,192 @@
         </is>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-45.530439205374066,170.76053756877326</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-45.53088521513244,170.75981193722305</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-45.531361187443856,170.75921383408797</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-45.531803424363495,170.75861537106582</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-45.532248963446264,170.75798203871187</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-45.53270868788102,170.75736079240144</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>-45.53318496934216,170.75676778954772</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>-45.533684677472536,170.7562179486677</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>-45.53419783866447,170.75570724457086</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>-45.53471244727441,170.75519223889887</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-45.53045234298348,170.76054625314288</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-45.53087933928612,170.75980517350467</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-45.53135121995498,170.75919783559516</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-45.5317965655325,170.75860650319956</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-45.532246272683345,170.75797863783396</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-45.532705747898184,170.75735683122718</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-45.53318217871995,170.7567637938921</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>-45.533677864480836,170.75620669805423</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>-45.53419273394704,170.755697489098</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>-45.534707061699244,170.75518166492034</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-45.53046711259333,170.7605560163209</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-45.530881158000504,170.75980726703642</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-45.53134560951119,170.75918883045802</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-45.53178091674092,170.75858627069724</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-45.53223941123747,170.75796996559677</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-45.532702219918605,170.7573520778187</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-45.53317862701876,170.75675870851282</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>-45.53367210867667,170.7561971932277</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>-45.534190638325974,170.75569348422016</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>-45.53470653370163,170.75518062825586</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L688"/>
+  <dimension ref="A1:L689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29318,6 +29318,48 @@
         <v>345.34</v>
       </c>
       <c r="L688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="C689" t="n">
+        <v>329.37</v>
+      </c>
+      <c r="D689" t="n">
+        <v>319.21</v>
+      </c>
+      <c r="E689" t="n">
+        <v>320.33</v>
+      </c>
+      <c r="F689" t="n">
+        <v>325.43</v>
+      </c>
+      <c r="G689" t="n">
+        <v>330.32</v>
+      </c>
+      <c r="H689" t="n">
+        <v>335.41</v>
+      </c>
+      <c r="I689" t="n">
+        <v>342.56</v>
+      </c>
+      <c r="J689" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="K689" t="n">
+        <v>344.79</v>
+      </c>
+      <c r="L689" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29334,7 +29376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B717"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36507,6 +36549,16 @@
       </c>
       <c r="B717" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>
@@ -36675,28 +36727,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.021172740277755</v>
+        <v>-1.000313189065005</v>
       </c>
       <c r="J2" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K2" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0157838984791917</v>
+        <v>0.0151724035804589</v>
       </c>
       <c r="M2" t="n">
-        <v>47.67665442370684</v>
+        <v>47.70401556278826</v>
       </c>
       <c r="N2" t="n">
-        <v>2981.333695878868</v>
+        <v>2983.116115118247</v>
       </c>
       <c r="O2" t="n">
-        <v>54.60159059843283</v>
+        <v>54.61791020460456</v>
       </c>
       <c r="P2" t="n">
-        <v>277.9226857553247</v>
+        <v>277.670852061535</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36753,28 +36805,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3219335109155256</v>
+        <v>-0.3211293192434763</v>
       </c>
       <c r="J3" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K3" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1157472590718361</v>
+        <v>0.1155316127219363</v>
       </c>
       <c r="M3" t="n">
-        <v>4.843684836848442</v>
+        <v>4.839989151830543</v>
       </c>
       <c r="N3" t="n">
-        <v>37.99140651556642</v>
+        <v>37.94602952963917</v>
       </c>
       <c r="O3" t="n">
-        <v>6.163716939928896</v>
+        <v>6.160034864320101</v>
       </c>
       <c r="P3" t="n">
-        <v>335.3430238314005</v>
+        <v>335.3335756974197</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36831,28 +36883,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3746687198670409</v>
+        <v>-0.373969486717002</v>
       </c>
       <c r="J4" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K4" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1537199590682214</v>
+        <v>0.1536180034734007</v>
       </c>
       <c r="M4" t="n">
-        <v>4.828504268700015</v>
+        <v>4.824657027208467</v>
       </c>
       <c r="N4" t="n">
-        <v>37.08224445603513</v>
+        <v>37.0357872674509</v>
       </c>
       <c r="O4" t="n">
-        <v>6.089519230286997</v>
+        <v>6.085703514586535</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9274673737825</v>
+        <v>326.9192523564988</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36909,28 +36961,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2965189052716489</v>
+        <v>-0.2958598572305542</v>
       </c>
       <c r="J5" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K5" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1009283728238084</v>
+        <v>0.1007947619082967</v>
       </c>
       <c r="M5" t="n">
-        <v>4.871778698341336</v>
+        <v>4.86764494522937</v>
       </c>
       <c r="N5" t="n">
-        <v>37.58141244224562</v>
+        <v>37.53339897562036</v>
       </c>
       <c r="O5" t="n">
-        <v>6.130368051124306</v>
+        <v>6.12645076497154</v>
       </c>
       <c r="P5" t="n">
-        <v>326.0926324667557</v>
+        <v>326.0848895686278</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36987,28 +37039,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3345459149694098</v>
+        <v>-0.3341566442994993</v>
       </c>
       <c r="J6" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K6" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1703372578489968</v>
+        <v>0.1704413277797463</v>
       </c>
       <c r="M6" t="n">
-        <v>4.119191693015925</v>
+        <v>4.11503130048978</v>
       </c>
       <c r="N6" t="n">
-        <v>26.15716668191483</v>
+        <v>26.12145384170597</v>
       </c>
       <c r="O6" t="n">
-        <v>5.114407754756638</v>
+        <v>5.110915166749098</v>
       </c>
       <c r="P6" t="n">
-        <v>333.0879155097716</v>
+        <v>333.0833421206507</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37065,28 +37117,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2177733267940236</v>
+        <v>-0.2176851301284466</v>
       </c>
       <c r="J7" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K7" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.12190676811483</v>
+        <v>0.1221570095077791</v>
       </c>
       <c r="M7" t="n">
-        <v>3.225411371528443</v>
+        <v>3.221138313237564</v>
       </c>
       <c r="N7" t="n">
-        <v>16.39115226222994</v>
+        <v>16.36744630335456</v>
       </c>
       <c r="O7" t="n">
-        <v>4.04859880233025</v>
+        <v>4.045670068524442</v>
       </c>
       <c r="P7" t="n">
-        <v>335.8394428234768</v>
+        <v>335.8384066352868</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37143,28 +37195,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08574984970761378</v>
+        <v>-0.08546682613857187</v>
       </c>
       <c r="J8" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K8" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03043427804393184</v>
+        <v>0.03032917992684192</v>
       </c>
       <c r="M8" t="n">
-        <v>2.708971207085156</v>
+        <v>2.706426686169884</v>
       </c>
       <c r="N8" t="n">
-        <v>11.24005109695115</v>
+        <v>11.2249329634079</v>
       </c>
       <c r="O8" t="n">
-        <v>3.352618543310758</v>
+        <v>3.350363109188003</v>
       </c>
       <c r="P8" t="n">
-        <v>336.775499276476</v>
+        <v>336.7721741430619</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37221,28 +37273,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06059583622354779</v>
+        <v>-0.05965834635758412</v>
       </c>
       <c r="J9" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K9" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01327189644503179</v>
+        <v>0.01289675205254681</v>
       </c>
       <c r="M9" t="n">
-        <v>2.900768115429734</v>
+        <v>2.900222825423473</v>
       </c>
       <c r="N9" t="n">
-        <v>13.09897704208252</v>
+        <v>13.09331441184247</v>
       </c>
       <c r="O9" t="n">
-        <v>3.619250895155311</v>
+        <v>3.618468517459074</v>
       </c>
       <c r="P9" t="n">
-        <v>341.13598521096</v>
+        <v>341.1249710085414</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37299,28 +37351,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04050562338499085</v>
+        <v>0.04146588578635246</v>
       </c>
       <c r="J10" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K10" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008029083888591249</v>
+        <v>0.008425311687121018</v>
       </c>
       <c r="M10" t="n">
-        <v>2.494187736461662</v>
+        <v>2.495085338802168</v>
       </c>
       <c r="N10" t="n">
-        <v>9.72637222387073</v>
+        <v>9.726269388538173</v>
       </c>
       <c r="O10" t="n">
-        <v>3.11871323206715</v>
+        <v>3.118696745202741</v>
       </c>
       <c r="P10" t="n">
-        <v>340.5506662144759</v>
+        <v>340.5393844664299</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37377,28 +37429,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05891426365435661</v>
+        <v>0.05867448968892055</v>
       </c>
       <c r="J11" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K11" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01833154723398023</v>
+        <v>0.0182399668346942</v>
       </c>
       <c r="M11" t="n">
-        <v>2.384571940121089</v>
+        <v>2.382179403485153</v>
       </c>
       <c r="N11" t="n">
-        <v>8.918543229407048</v>
+        <v>8.906455246534364</v>
       </c>
       <c r="O11" t="n">
-        <v>2.986393013219634</v>
+        <v>2.984368483705449</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9971201064295</v>
+        <v>343.9999371171364</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37436,7 +37488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L688"/>
+  <dimension ref="A1:L689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80047,6 +80099,68 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-45.53047184539632,170.7605591448541</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-45.53087374324165,170.75979873186944</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-45.5313306881148,170.7591648806339</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-45.531762737502135,170.7585627665703</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-45.532215328902865,170.75793952776132</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-45.53268333869142,170.75732663829052</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-45.533166259486144,170.7567410005006</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>-45.53367069909186,170.7561948655154</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>-45.534187521761055,170.7556875282486</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>-45.53470362971458,170.75517492660174</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L689"/>
+  <dimension ref="A1:L695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29330,7 +29330,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>315.55</v>
+        <v>302.24</v>
       </c>
       <c r="C689" t="n">
         <v>329.37</v>
@@ -29360,6 +29360,258 @@
         <v>344.79</v>
       </c>
       <c r="L689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>288.32</v>
+      </c>
+      <c r="C690" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="D690" t="n">
+        <v>317.95</v>
+      </c>
+      <c r="E690" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="F690" t="n">
+        <v>324.37</v>
+      </c>
+      <c r="G690" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="H690" t="n">
+        <v>333.45</v>
+      </c>
+      <c r="I690" t="n">
+        <v>341.48</v>
+      </c>
+      <c r="J690" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="K690" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>267.76</v>
+      </c>
+      <c r="C691" t="n">
+        <v>322.13</v>
+      </c>
+      <c r="D691" t="n">
+        <v>314.41</v>
+      </c>
+      <c r="E691" t="n">
+        <v>316.37</v>
+      </c>
+      <c r="F691" t="n">
+        <v>321.39</v>
+      </c>
+      <c r="G691" t="n">
+        <v>327.59</v>
+      </c>
+      <c r="H691" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="I691" t="n">
+        <v>340.09</v>
+      </c>
+      <c r="J691" t="n">
+        <v>343.12</v>
+      </c>
+      <c r="K691" t="n">
+        <v>345.72</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>255.95</v>
+      </c>
+      <c r="C692" t="n">
+        <v>320.87</v>
+      </c>
+      <c r="D692" t="n">
+        <v>315.18</v>
+      </c>
+      <c r="E692" t="n">
+        <v>317.13</v>
+      </c>
+      <c r="F692" t="n">
+        <v>321.97</v>
+      </c>
+      <c r="G692" t="n">
+        <v>327.57</v>
+      </c>
+      <c r="H692" t="n">
+        <v>331.56</v>
+      </c>
+      <c r="I692" t="n">
+        <v>339.72</v>
+      </c>
+      <c r="J692" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="K692" t="n">
+        <v>346.89</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>241.56</v>
+      </c>
+      <c r="C693" t="n">
+        <v>320.33</v>
+      </c>
+      <c r="D693" t="n">
+        <v>313.23</v>
+      </c>
+      <c r="E693" t="n">
+        <v>315.53</v>
+      </c>
+      <c r="F693" t="n">
+        <v>321.11</v>
+      </c>
+      <c r="G693" t="n">
+        <v>327.06</v>
+      </c>
+      <c r="H693" t="n">
+        <v>330.92</v>
+      </c>
+      <c r="I693" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="J693" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="K693" t="n">
+        <v>346.67</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>224.43</v>
+      </c>
+      <c r="C694" t="n">
+        <v>318.98</v>
+      </c>
+      <c r="D694" t="n">
+        <v>314.29</v>
+      </c>
+      <c r="E694" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="F694" t="n">
+        <v>322.33</v>
+      </c>
+      <c r="G694" t="n">
+        <v>327.22</v>
+      </c>
+      <c r="H694" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="I694" t="n">
+        <v>340.59</v>
+      </c>
+      <c r="J694" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="K694" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>216.18</v>
+      </c>
+      <c r="C695" t="n">
+        <v>318.98</v>
+      </c>
+      <c r="D695" t="n">
+        <v>315.08</v>
+      </c>
+      <c r="E695" t="n">
+        <v>317.15</v>
+      </c>
+      <c r="F695" t="n">
+        <v>323.24</v>
+      </c>
+      <c r="G695" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="H695" t="n">
+        <v>333.36</v>
+      </c>
+      <c r="I695" t="n">
+        <v>341.05</v>
+      </c>
+      <c r="J695" t="n">
+        <v>345.27</v>
+      </c>
+      <c r="K695" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="L695" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29376,7 +29628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36559,6 +36811,66 @@
       </c>
       <c r="B718" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -36727,28 +37039,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.000313189065005</v>
+        <v>-1.008199682720596</v>
       </c>
       <c r="J2" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K2" t="n">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0151724035804589</v>
+        <v>0.01568547554696165</v>
       </c>
       <c r="M2" t="n">
-        <v>47.70401556278826</v>
+        <v>47.45413981088156</v>
       </c>
       <c r="N2" t="n">
-        <v>2983.116115118247</v>
+        <v>2960.029148808019</v>
       </c>
       <c r="O2" t="n">
-        <v>54.61791020460456</v>
+        <v>54.40614991715568</v>
       </c>
       <c r="P2" t="n">
-        <v>277.670852061535</v>
+        <v>277.7666778920888</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36805,28 +37117,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3211293192434763</v>
+        <v>-0.3308607666808692</v>
       </c>
       <c r="J3" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K3" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1155316127219363</v>
+        <v>0.1229120906623915</v>
       </c>
       <c r="M3" t="n">
-        <v>4.839989151830543</v>
+        <v>4.850552306430343</v>
       </c>
       <c r="N3" t="n">
-        <v>37.94602952963917</v>
+        <v>37.92525981146954</v>
       </c>
       <c r="O3" t="n">
-        <v>6.160034864320101</v>
+        <v>6.158348789364689</v>
       </c>
       <c r="P3" t="n">
-        <v>335.3335756974197</v>
+        <v>335.4482136987251</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36883,28 +37195,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.373969486717002</v>
+        <v>-0.377421511257615</v>
       </c>
       <c r="J4" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K4" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1536180034734007</v>
+        <v>0.1583282456183284</v>
       </c>
       <c r="M4" t="n">
-        <v>4.824657027208467</v>
+        <v>4.802675708760889</v>
       </c>
       <c r="N4" t="n">
-        <v>37.0357872674509</v>
+        <v>36.76437223583671</v>
       </c>
       <c r="O4" t="n">
-        <v>6.085703514586535</v>
+        <v>6.063363112649341</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9192523564988</v>
+        <v>326.9599183212905</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36961,28 +37273,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2958598572305542</v>
+        <v>-0.2980053411349868</v>
       </c>
       <c r="J5" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K5" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1007947619082967</v>
+        <v>0.1037802891130005</v>
       </c>
       <c r="M5" t="n">
-        <v>4.86764494522937</v>
+        <v>4.839846910798196</v>
       </c>
       <c r="N5" t="n">
-        <v>37.53339897562036</v>
+        <v>37.23378731511605</v>
       </c>
       <c r="O5" t="n">
-        <v>6.12645076497154</v>
+        <v>6.101949468417126</v>
       </c>
       <c r="P5" t="n">
-        <v>326.0848895686278</v>
+        <v>326.1101675437365</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37039,28 +37351,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3341566442994993</v>
+        <v>-0.3373373997021437</v>
       </c>
       <c r="J6" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K6" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1704413277797463</v>
+        <v>0.1756305235773584</v>
       </c>
       <c r="M6" t="n">
-        <v>4.11503130048978</v>
+        <v>4.095017739307227</v>
       </c>
       <c r="N6" t="n">
-        <v>26.12145384170597</v>
+        <v>25.93226168515075</v>
       </c>
       <c r="O6" t="n">
-        <v>5.110915166749098</v>
+        <v>5.092372893372081</v>
       </c>
       <c r="P6" t="n">
-        <v>333.0833421206507</v>
+        <v>333.1208004362786</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37117,28 +37429,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2176851301284466</v>
+        <v>-0.2218938784045888</v>
       </c>
       <c r="J7" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K7" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1221570095077791</v>
+        <v>0.1280611797522851</v>
       </c>
       <c r="M7" t="n">
-        <v>3.221138313237564</v>
+        <v>3.212940013955337</v>
       </c>
       <c r="N7" t="n">
-        <v>16.36744630335456</v>
+        <v>16.27603668679673</v>
       </c>
       <c r="O7" t="n">
-        <v>4.045670068524442</v>
+        <v>4.034357035116839</v>
       </c>
       <c r="P7" t="n">
-        <v>335.8384066352868</v>
+        <v>335.8879759509803</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37195,28 +37507,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08546682613857187</v>
+        <v>-0.08969177820109361</v>
       </c>
       <c r="J8" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K8" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03032917992684192</v>
+        <v>0.03374891845904682</v>
       </c>
       <c r="M8" t="n">
-        <v>2.706426686169884</v>
+        <v>2.701793768825644</v>
       </c>
       <c r="N8" t="n">
-        <v>11.2249329634079</v>
+        <v>11.18213946592558</v>
       </c>
       <c r="O8" t="n">
-        <v>3.350363109188003</v>
+        <v>3.34397061379516</v>
       </c>
       <c r="P8" t="n">
-        <v>336.7721741430619</v>
+        <v>336.8219218924561</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37273,28 +37585,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05965834635758412</v>
+        <v>-0.05813994120179763</v>
       </c>
       <c r="J9" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K9" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01289675205254681</v>
+        <v>0.0124751217125596</v>
       </c>
       <c r="M9" t="n">
-        <v>2.900222825423473</v>
+        <v>2.881782300377979</v>
       </c>
       <c r="N9" t="n">
-        <v>13.09331441184247</v>
+        <v>12.99098056477375</v>
       </c>
       <c r="O9" t="n">
-        <v>3.618468517459074</v>
+        <v>3.604300287819225</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1249710085414</v>
+        <v>341.1070928607063</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37351,28 +37663,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04146588578635246</v>
+        <v>0.046088344471343</v>
       </c>
       <c r="J10" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K10" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008425311687121018</v>
+        <v>0.01051876174342459</v>
       </c>
       <c r="M10" t="n">
-        <v>2.495085338802168</v>
+        <v>2.495269903261542</v>
       </c>
       <c r="N10" t="n">
-        <v>9.726269388538173</v>
+        <v>9.700958903527615</v>
       </c>
       <c r="O10" t="n">
-        <v>3.118696745202741</v>
+        <v>3.114636239358878</v>
       </c>
       <c r="P10" t="n">
-        <v>340.5393844664299</v>
+        <v>340.4849446615398</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37429,28 +37741,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05867448968892055</v>
+        <v>0.06093354551488827</v>
       </c>
       <c r="J11" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="K11" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0182399668346942</v>
+        <v>0.01995193229544356</v>
       </c>
       <c r="M11" t="n">
-        <v>2.382179403485153</v>
+        <v>2.373972397701582</v>
       </c>
       <c r="N11" t="n">
-        <v>8.906455246534364</v>
+        <v>8.854515752850221</v>
       </c>
       <c r="O11" t="n">
-        <v>2.984368483705449</v>
+        <v>2.975653836193017</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9999371171364</v>
+        <v>343.9733141724873</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37488,7 +37800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L689"/>
+  <dimension ref="A1:L695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80107,7 +80419,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>-45.53047184539632,170.7605591448541</t>
+          <t>-45.53036323570767,170.7604873505395</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -80156,6 +80468,378 @@
         </is>
       </c>
       <c r="L689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-45.53024964837019,170.760412266166</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-45.53085723490846,170.75977972905287</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-45.531323167729205,170.75915280992737</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-45.531757010708006,170.75855536234297</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-45.53220819837773,170.75793051544628</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-45.5326766747276,170.75731765963758</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-45.53315382852765,170.7567232016859</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>-45.53366435595965,170.7561843908114</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>-45.53418247077588,170.75567787546848</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>-45.534705424906605,170.75517845126058</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-45.530081878483436,170.7603013662241</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-45.53082309902353,170.7597404351283</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-45.53130203902025,170.75911889700726</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-45.53173636760912,170.75852867269876</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-45.53218815218081,170.75790517895018</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-45.53266550278672,170.7573026071948</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>-45.533140002254356,170.75670340505428</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>-45.53365619211221,170.75617090948293</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>-45.534178763137334,170.75567078991824</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>-45.53470854009252,170.7551845675809</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-45.52998550867359,170.76023766377668</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-45.53081428524788,170.75973028957347</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-45.531306634813696,170.7591262735442</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-45.53174142849843,170.75853521596457</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-45.53219205379001,170.75791011021315</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-45.53266537212074,170.75730243114285</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>-45.53314184152944,170.75670603855062</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>-45.533654019001496,170.7561673209285</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>-45.53418558734129,170.755683831439</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>-45.53471471766364,170.7551966965571</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-45.52986808597337,170.76016004524817</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-45.53081050791519,170.7597259414795</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-45.5312949961151,170.75910759270621</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-45.53173077399419,170.75852144066948</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-45.53218626864524,170.75790279834075</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-45.532662040138,170.75729794181896</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>-45.53313778243954,170.7567002266969</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>-45.533651434761566,170.75616305345878</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>-45.5341833305181,170.75567951849476</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>-45.534713556069185,170.75519441589472</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-45.52972830475224,170.760067647787</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-45.53080106458281,170.75971507124714</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-45.53130132279264,170.75911774741718</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-45.531736034655864,170.7585282422208</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-45.5321944754784,170.75791317099737</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-45.532663085465934,170.75729935023426</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>-45.533146978814685,170.75671339417912</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>-45.53365912874817,170.75617575888123</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>-45.53418698442224,170.75568650135702</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>-45.53472005043773,170.75520716687205</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-45.5296609845247,170.7600231482938</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-45.53080106458281,170.75971507124714</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-45.53130603795742,170.75912531555232</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-45.53174156167973,170.7585353881558</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-45.53220059696812,170.7579209079809</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-45.53266458812481,170.7573013748313</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>-45.53315325771827,170.75672238439358</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>-45.53366183045306,170.75618022032808</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>-45.53419031592272,170.75569286808516</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>-45.534723588020015,170.75521411252763</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0493/nzd0493.xlsx
+++ b/data/nzd0493/nzd0493.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L695"/>
+  <dimension ref="A1:L699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29612,6 +29612,174 @@
         <v>348.57</v>
       </c>
       <c r="L695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>201.2</v>
+      </c>
+      <c r="C696" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="D696" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="E696" t="n">
+        <v>314.53</v>
+      </c>
+      <c r="F696" t="n">
+        <v>319.04</v>
+      </c>
+      <c r="G696" t="n">
+        <v>325.68</v>
+      </c>
+      <c r="H696" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="I696" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="J696" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="K696" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>197.65</v>
+      </c>
+      <c r="C697" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="D697" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="E697" t="n">
+        <v>313.64</v>
+      </c>
+      <c r="F697" t="n">
+        <v>318.93</v>
+      </c>
+      <c r="G697" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="H697" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="I697" t="n">
+        <v>339.09</v>
+      </c>
+      <c r="J697" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="K697" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>197.65</v>
+      </c>
+      <c r="C698" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="D698" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="E698" t="n">
+        <v>311.43</v>
+      </c>
+      <c r="F698" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="G698" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="H698" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="I698" t="n">
+        <v>339.09</v>
+      </c>
+      <c r="J698" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="K698" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>192.69</v>
+      </c>
+      <c r="C699" t="n">
+        <v>315.55</v>
+      </c>
+      <c r="D699" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="E699" t="n">
+        <v>311.05</v>
+      </c>
+      <c r="F699" t="n">
+        <v>319.6</v>
+      </c>
+      <c r="G699" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="H699" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="I699" t="n">
+        <v>338.91</v>
+      </c>
+      <c r="J699" t="n">
+        <v>342.04</v>
+      </c>
+      <c r="K699" t="n">
+        <v>348.12</v>
+      </c>
+      <c r="L699" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29628,7 +29796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B724"/>
+  <dimension ref="A1:B729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36871,6 +37039,56 @@
       </c>
       <c r="B724" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -37039,28 +37257,28 @@
         <v>0.1115</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.008199682720596</v>
+        <v>-1.074896729707986</v>
       </c>
       <c r="J2" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K2" t="n">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01568547554696165</v>
+        <v>0.01791551993819485</v>
       </c>
       <c r="M2" t="n">
-        <v>47.45413981088156</v>
+        <v>47.4795289594152</v>
       </c>
       <c r="N2" t="n">
-        <v>2960.029148808019</v>
+        <v>2959.162126731403</v>
       </c>
       <c r="O2" t="n">
-        <v>54.40614991715568</v>
+        <v>54.39818128146752</v>
       </c>
       <c r="P2" t="n">
-        <v>277.7666778920888</v>
+        <v>278.5769278888338</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37117,28 +37335,28 @@
         <v>0.0825</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3308607666808692</v>
+        <v>-0.3440626489404776</v>
       </c>
       <c r="J3" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K3" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1229120906623915</v>
+        <v>0.130960167637488</v>
       </c>
       <c r="M3" t="n">
-        <v>4.850552306430343</v>
+        <v>4.892642097768827</v>
       </c>
       <c r="N3" t="n">
-        <v>37.92525981146954</v>
+        <v>38.39214210569538</v>
       </c>
       <c r="O3" t="n">
-        <v>6.158348789364689</v>
+        <v>6.196139290372303</v>
       </c>
       <c r="P3" t="n">
-        <v>335.4482136987251</v>
+        <v>335.6043136403254</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37195,28 +37413,28 @@
         <v>0.0639</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.377421511257615</v>
+        <v>-0.3808960500778246</v>
       </c>
       <c r="J4" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K4" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1583282456183284</v>
+        <v>0.1622861756196939</v>
       </c>
       <c r="M4" t="n">
-        <v>4.802675708760889</v>
+        <v>4.791893813855615</v>
       </c>
       <c r="N4" t="n">
-        <v>36.76437223583671</v>
+        <v>36.60108175278157</v>
       </c>
       <c r="O4" t="n">
-        <v>6.063363112649341</v>
+        <v>6.049882788350661</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9599183212905</v>
+        <v>327.0010014815719</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37273,28 +37491,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2980053411349868</v>
+        <v>-0.3045376963962909</v>
       </c>
       <c r="J5" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K5" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1037802891130005</v>
+        <v>0.1086106823639813</v>
       </c>
       <c r="M5" t="n">
-        <v>4.839846910798196</v>
+        <v>4.844150445426432</v>
       </c>
       <c r="N5" t="n">
-        <v>37.23378731511605</v>
+        <v>37.20007592603489</v>
       </c>
       <c r="O5" t="n">
-        <v>6.101949468417126</v>
+        <v>6.099186497069498</v>
       </c>
       <c r="P5" t="n">
-        <v>326.1101675437365</v>
+        <v>326.1874155404522</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37351,28 +37569,28 @@
         <v>0.0944</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3373373997021437</v>
+        <v>-0.3430896200999178</v>
       </c>
       <c r="J6" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K6" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1756305235773584</v>
+        <v>0.1816672643190057</v>
       </c>
       <c r="M6" t="n">
-        <v>4.095017739307227</v>
+        <v>4.098790383137534</v>
       </c>
       <c r="N6" t="n">
-        <v>25.93226168515075</v>
+        <v>25.91404645719376</v>
       </c>
       <c r="O6" t="n">
-        <v>5.092372893372081</v>
+        <v>5.090584097841206</v>
       </c>
       <c r="P6" t="n">
-        <v>333.1208004362786</v>
+        <v>333.1888133343113</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37429,28 +37647,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2218938784045888</v>
+        <v>-0.2269047668094723</v>
       </c>
       <c r="J7" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K7" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1280611797522851</v>
+        <v>0.1338602254697098</v>
       </c>
       <c r="M7" t="n">
-        <v>3.212940013955337</v>
+        <v>3.217679643273843</v>
       </c>
       <c r="N7" t="n">
-        <v>16.27603668679673</v>
+        <v>16.28135314607846</v>
       </c>
       <c r="O7" t="n">
-        <v>4.034357035116839</v>
+        <v>4.035015879284548</v>
       </c>
       <c r="P7" t="n">
-        <v>335.8879759509803</v>
+        <v>335.9472249378404</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37507,28 +37725,28 @@
         <v>0.1156</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08969177820109361</v>
+        <v>-0.09449693370774857</v>
       </c>
       <c r="J8" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K8" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03374891845904682</v>
+        <v>0.03747498598882548</v>
       </c>
       <c r="M8" t="n">
-        <v>2.701793768825644</v>
+        <v>2.707292684732709</v>
       </c>
       <c r="N8" t="n">
-        <v>11.18213946592558</v>
+        <v>11.20915321031233</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34397061379516</v>
+        <v>3.348007349202258</v>
       </c>
       <c r="P8" t="n">
-        <v>336.8219218924561</v>
+        <v>336.8787397306321</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37585,28 +37803,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05813994120179763</v>
+        <v>-0.05877104691323379</v>
       </c>
       <c r="J9" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K9" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0124751217125596</v>
+        <v>0.01289899044191645</v>
       </c>
       <c r="M9" t="n">
-        <v>2.881782300377979</v>
+        <v>2.868781089703336</v>
       </c>
       <c r="N9" t="n">
-        <v>12.99098056477375</v>
+        <v>12.91812718171068</v>
       </c>
       <c r="O9" t="n">
-        <v>3.604300287819225</v>
+        <v>3.594179625687993</v>
       </c>
       <c r="P9" t="n">
-        <v>341.1070928607063</v>
+        <v>341.1145552320149</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37663,28 +37881,28 @@
         <v>0.1026</v>
       </c>
       <c r="I10" t="n">
-        <v>0.046088344471343</v>
+        <v>0.04728212097558261</v>
       </c>
       <c r="J10" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K10" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01051876174342459</v>
+        <v>0.01119321277908447</v>
       </c>
       <c r="M10" t="n">
-        <v>2.495269903261542</v>
+        <v>2.486514382116718</v>
       </c>
       <c r="N10" t="n">
-        <v>9.700958903527615</v>
+        <v>9.652002051250157</v>
       </c>
       <c r="O10" t="n">
-        <v>3.114636239358878</v>
+        <v>3.106767138240354</v>
       </c>
       <c r="P10" t="n">
-        <v>340.4849446615398</v>
+        <v>340.470831405667</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37741,28 +37959,28 @@
         <v>0.1391</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06093354551488827</v>
+        <v>0.06379367093657229</v>
       </c>
       <c r="J11" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="K11" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01995193229544356</v>
+        <v>0.02201420064300519</v>
       </c>
       <c r="M11" t="n">
-        <v>2.373972397701582</v>
+        <v>2.374316941763314</v>
       </c>
       <c r="N11" t="n">
-        <v>8.854515752850221</v>
+        <v>8.835917306829346</v>
       </c>
       <c r="O11" t="n">
-        <v>2.975653836193017</v>
+        <v>2.972527091016892</v>
       </c>
       <c r="P11" t="n">
-        <v>343.9733141724873</v>
+        <v>343.9394955738852</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37800,7 +38018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L695"/>
+  <dimension ref="A1:L699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80845,6 +81063,254 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-45.529538747270465,170.75994234826732</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-45.53077707151906,170.75968745282125</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-45.53129923379544,170.75911439444633</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-45.53172411492827,170.7585128311127</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-45.53217234393447,170.7578851988401</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-45.532653024183865,170.75728579423938</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>-45.53313740189984,170.75669968183567</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>-45.53364973151244,170.75616024080847</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>-45.53417930047629,170.75567181680952</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>-45.53472036723616,170.75520778887102</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>-45.52950977915505,170.75992320011363</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>-45.53077707151906,170.75968745282125</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-45.53129923379544,170.75911439444633</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-45.53171818835906,170.75850516860888</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-45.53217160397393,170.7578842636012</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>-45.53265380817992,170.75728685055049</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>-45.533134103889076,170.75669495970521</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>-45.53365031883973,170.75616121068788</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>-45.534177043652655,170.75566750386625</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>-45.53472031443641,170.7552076852045</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>-45.52950977915505,170.75992320011363</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>-45.53077707151906,170.75968745282125</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-45.53129923379544,170.75911439444633</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-45.5317034718199,170.75848614149956</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>-45.532175438314866,170.7578891098395</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>-45.53265380817992,170.75728685055049</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>-45.533134103889076,170.75669495970521</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>-45.53365031883973,170.75616121068788</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>-45.534177043652655,170.75566750386625</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>-45.53472031443641,170.7552076852045</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>-45.5294693053888,170.7598964466691</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>-45.53077707151906,170.75968745282125</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>-45.53129923379544,170.75911439444633</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>-45.531700941373956,170.7584828698709</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>-45.53217611100624,170.75788996005681</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>-45.53265335084889,170.75728623436902</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>-45.533132454883614,170.7566925986402</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>-45.533649261650595,170.75615946490498</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>-45.53417295987616,170.75565969949363</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>-45.53472121203195,170.75520944753498</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
